--- a/Bdd_reunion.xlsx
+++ b/Bdd_reunion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projet_Pennylane\Emargement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C7BE84-14F0-43BE-8F8C-C2832C5AD1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D020F4B-E60F-46B9-B30F-7E60F82BF745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{C4CEBAE8-6564-4A3B-9673-9C165A296274}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4CEBAE8-6564-4A3B-9673-9C165A296274}"/>
   </bookViews>
   <sheets>
     <sheet name="Reunions" sheetId="1" r:id="rId1"/>
@@ -5440,7 +5440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -5491,7 +5491,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -5525,7 +5525,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>5</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>5</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>5</v>
       </c>
@@ -5627,7 +5627,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>5</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>5</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>5</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>5</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>5</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>5</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>5</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>5</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>5</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>5</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
@@ -5865,7 +5865,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>5</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>5</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>5</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>5</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>5</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>5</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>5</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>5</v>
       </c>
@@ -6035,7 +6035,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>5</v>
       </c>
@@ -6052,7 +6052,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>5</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>5</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>5</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>5</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -6137,7 +6137,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -6154,7 +6154,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -6222,7 +6222,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -6239,7 +6239,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -6256,7 +6256,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -6324,7 +6324,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -6375,7 +6375,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -6409,7 +6409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -6426,7 +6426,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -6477,7 +6477,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -6511,7 +6511,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -6528,7 +6528,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -6579,7 +6579,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -6596,7 +6596,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -6630,7 +6630,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -6647,7 +6647,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -6681,7 +6681,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -6749,7 +6749,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -6783,7 +6783,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -6817,7 +6817,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -6936,7 +6936,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -6970,7 +6970,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -6987,7 +6987,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -7021,7 +7021,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -7123,7 +7123,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -7174,7 +7174,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -7191,7 +7191,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -7208,7 +7208,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -7259,7 +7259,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -7378,7 +7378,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -7429,7 +7429,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>5</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>5</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>5</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>5</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>5</v>
       </c>
@@ -7565,7 +7565,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>5</v>
       </c>
@@ -7582,7 +7582,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
         <v>5</v>
       </c>
@@ -7599,7 +7599,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
         <v>5</v>
       </c>
@@ -7616,7 +7616,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
         <v>5</v>
       </c>
@@ -7633,7 +7633,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
         <v>5</v>
       </c>
@@ -7650,7 +7650,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
         <v>5</v>
       </c>
@@ -7667,7 +7667,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
         <v>5</v>
       </c>
@@ -7684,7 +7684,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>5</v>
       </c>
@@ -7701,7 +7701,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>5</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>5</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>5</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>5</v>
       </c>
@@ -7769,7 +7769,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>5</v>
       </c>
@@ -7786,7 +7786,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>5</v>
       </c>
@@ -7803,7 +7803,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>5</v>
       </c>
@@ -7820,7 +7820,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>5</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>5</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>5</v>
       </c>
@@ -7871,7 +7871,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>5</v>
       </c>
@@ -7888,7 +7888,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>5</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>5</v>
       </c>
@@ -7922,7 +7922,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>5</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>5</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>5</v>
       </c>
@@ -7973,7 +7973,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>5</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>5</v>
       </c>
@@ -8007,7 +8007,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>5</v>
       </c>
@@ -8024,7 +8024,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>5</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>5</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>5</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>5</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>5</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>5</v>
       </c>
@@ -8126,7 +8126,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>5</v>
       </c>
@@ -8143,7 +8143,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>5</v>
       </c>
@@ -8160,7 +8160,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>5</v>
       </c>
@@ -8177,7 +8177,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>5</v>
       </c>
@@ -8194,7 +8194,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>5</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>5</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
         <v>5</v>
       </c>
@@ -8245,7 +8245,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
         <v>5</v>
       </c>
@@ -8262,7 +8262,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
         <v>5</v>
       </c>
@@ -8279,7 +8279,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>5</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
         <v>5</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
         <v>5</v>
       </c>
@@ -8330,7 +8330,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
         <v>5</v>
       </c>
@@ -8347,7 +8347,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
         <v>5</v>
       </c>
@@ -8364,7 +8364,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
         <v>5</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
         <v>5</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
         <v>5</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
         <v>5</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
         <v>5</v>
       </c>
@@ -8449,7 +8449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
         <v>5</v>
       </c>
@@ -8466,7 +8466,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
         <v>5</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>5</v>
       </c>
@@ -8500,7 +8500,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
         <v>5</v>
       </c>
@@ -8517,7 +8517,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
         <v>5</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
         <v>5</v>
       </c>
@@ -8551,7 +8551,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
         <v>5</v>
       </c>
@@ -8568,7 +8568,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
         <v>5</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
         <v>5</v>
       </c>
@@ -8602,7 +8602,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
         <v>5</v>
       </c>
@@ -8619,7 +8619,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
         <v>5</v>
       </c>
@@ -8636,7 +8636,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
         <v>5</v>
       </c>
@@ -8653,7 +8653,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
         <v>5</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
         <v>5</v>
       </c>
@@ -8687,7 +8687,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
         <v>5</v>
       </c>
@@ -8704,7 +8704,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
         <v>5</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
         <v>5</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
         <v>5</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
         <v>5</v>
       </c>
@@ -8772,7 +8772,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
         <v>5</v>
       </c>
@@ -8789,7 +8789,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
         <v>5</v>
       </c>
@@ -8806,7 +8806,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
         <v>5</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
         <v>5</v>
       </c>
@@ -8840,7 +8840,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
         <v>5</v>
       </c>
@@ -8857,7 +8857,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>5</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
         <v>5</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
         <v>5</v>
       </c>
@@ -8908,7 +8908,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
         <v>5</v>
       </c>
@@ -8925,7 +8925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>5</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
         <v>5</v>
       </c>
@@ -8959,7 +8959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
         <v>5</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
         <v>5</v>
       </c>
@@ -8993,7 +8993,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
         <v>5</v>
       </c>
@@ -9010,7 +9010,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
         <v>5</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
         <v>5</v>
       </c>
@@ -9044,7 +9044,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
         <v>5</v>
       </c>
@@ -9061,7 +9061,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>5</v>
       </c>
@@ -9078,7 +9078,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
         <v>5</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>5</v>
       </c>
@@ -9112,7 +9112,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
         <v>5</v>
       </c>
@@ -9129,7 +9129,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
         <v>5</v>
       </c>
@@ -9146,7 +9146,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
         <v>5</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
         <v>5</v>
       </c>
@@ -9180,7 +9180,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
         <v>5</v>
       </c>
@@ -9197,7 +9197,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="s">
         <v>5</v>
       </c>
@@ -9214,7 +9214,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
         <v>5</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
         <v>5</v>
       </c>
@@ -9248,7 +9248,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
         <v>5</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
         <v>5</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
         <v>5</v>
       </c>
@@ -9299,7 +9299,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
         <v>5</v>
       </c>
@@ -9316,7 +9316,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
         <v>5</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
         <v>5</v>
       </c>
@@ -9350,7 +9350,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
         <v>5</v>
       </c>
@@ -9367,7 +9367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>5</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
         <v>5</v>
       </c>
@@ -9401,7 +9401,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>5</v>
       </c>
@@ -9418,7 +9418,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
         <v>5</v>
       </c>
@@ -9435,7 +9435,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
         <v>5</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
         <v>5</v>
       </c>
@@ -9469,7 +9469,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>5</v>
       </c>
@@ -9486,7 +9486,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
         <v>5</v>
       </c>
@@ -9503,7 +9503,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
         <v>5</v>
       </c>
@@ -9520,7 +9520,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
         <v>5</v>
       </c>
@@ -9537,7 +9537,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>5</v>
       </c>
@@ -9554,7 +9554,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
         <v>5</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>5</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
         <v>5</v>
       </c>
@@ -9605,7 +9605,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>5</v>
       </c>
@@ -9622,7 +9622,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
         <v>5</v>
       </c>
@@ -9639,7 +9639,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>5</v>
       </c>
@@ -9656,7 +9656,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
         <v>5</v>
       </c>
@@ -9673,7 +9673,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>5</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>5</v>
       </c>
@@ -9707,7 +9707,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>5</v>
       </c>
@@ -9724,7 +9724,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
         <v>5</v>
       </c>
@@ -9741,7 +9741,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>5</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
         <v>5</v>
       </c>
@@ -9775,7 +9775,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>5</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>5</v>
       </c>
@@ -9809,7 +9809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
         <v>5</v>
       </c>
@@ -9826,7 +9826,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
         <v>5</v>
       </c>
@@ -9843,7 +9843,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>5</v>
       </c>
@@ -9860,7 +9860,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
         <v>5</v>
       </c>
@@ -9877,7 +9877,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
         <v>5</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>5</v>
       </c>
@@ -9911,7 +9911,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
         <v>5</v>
       </c>
@@ -9928,7 +9928,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
         <v>5</v>
       </c>
@@ -9945,7 +9945,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>5</v>
       </c>
@@ -9962,7 +9962,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
         <v>5</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>5</v>
       </c>
@@ -9996,7 +9996,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>5</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>5</v>
       </c>
@@ -10030,7 +10030,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
         <v>5</v>
       </c>
@@ -10047,7 +10047,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
         <v>5</v>
       </c>
@@ -10064,7 +10064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
         <v>5</v>
       </c>
@@ -10081,7 +10081,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>5</v>
       </c>
@@ -10098,7 +10098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
         <v>5</v>
       </c>
@@ -10115,7 +10115,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>5</v>
       </c>
@@ -10132,7 +10132,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>5</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>5</v>
       </c>
@@ -10166,7 +10166,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>5</v>
       </c>
@@ -10183,7 +10183,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>5</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>5</v>
       </c>
@@ -10217,7 +10217,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>5</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>5</v>
       </c>
@@ -10251,7 +10251,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>5</v>
       </c>
@@ -10268,7 +10268,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
         <v>5</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>5</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
         <v>5</v>
       </c>
@@ -10319,7 +10319,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>5</v>
       </c>
@@ -10336,7 +10336,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
         <v>5</v>
       </c>
@@ -10353,7 +10353,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>5</v>
       </c>
@@ -10370,7 +10370,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
         <v>5</v>
       </c>
@@ -10387,7 +10387,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A293" s="12" t="s">
         <v>306</v>
       </c>
@@ -10404,7 +10404,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
         <v>306</v>
       </c>
@@ -10421,7 +10421,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>306</v>
       </c>
@@ -10438,7 +10438,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
         <v>306</v>
       </c>
@@ -10455,7 +10455,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
         <v>306</v>
       </c>
@@ -10472,7 +10472,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
         <v>306</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
         <v>306</v>
       </c>
@@ -10506,7 +10506,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
         <v>306</v>
       </c>
@@ -10523,7 +10523,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
         <v>306</v>
       </c>
@@ -10540,7 +10540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
         <v>306</v>
       </c>
@@ -10557,7 +10557,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
         <v>306</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
         <v>306</v>
       </c>
@@ -10591,7 +10591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
         <v>306</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
         <v>306</v>
       </c>
@@ -10625,7 +10625,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
         <v>306</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
         <v>306</v>
       </c>
@@ -10659,7 +10659,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
         <v>306</v>
       </c>
@@ -10676,7 +10676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
         <v>306</v>
       </c>
@@ -10693,7 +10693,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
         <v>306</v>
       </c>
@@ -10710,7 +10710,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A312" s="4" t="s">
         <v>306</v>
       </c>
@@ -10727,7 +10727,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A313" s="4" t="s">
         <v>306</v>
       </c>
@@ -10744,7 +10744,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A314" s="4" t="s">
         <v>306</v>
       </c>
@@ -10761,7 +10761,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A315" s="4" t="s">
         <v>306</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A316" s="4" t="s">
         <v>306</v>
       </c>
@@ -10795,7 +10795,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A317" s="4" t="s">
         <v>306</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
         <v>306</v>
       </c>
@@ -10829,7 +10829,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
         <v>306</v>
       </c>
@@ -10846,7 +10846,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
         <v>306</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
         <v>306</v>
       </c>
@@ -10880,7 +10880,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A322" s="4" t="s">
         <v>306</v>
       </c>
@@ -10897,7 +10897,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A323" s="4" t="s">
         <v>306</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A324" s="4" t="s">
         <v>306</v>
       </c>
@@ -10931,7 +10931,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A325" s="4" t="s">
         <v>306</v>
       </c>
@@ -10948,7 +10948,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
         <v>306</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
         <v>306</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
         <v>306</v>
       </c>
@@ -10999,7 +10999,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
         <v>306</v>
       </c>
@@ -11016,7 +11016,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
         <v>306</v>
       </c>
@@ -11033,7 +11033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
         <v>306</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
         <v>306</v>
       </c>
@@ -11067,7 +11067,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
         <v>306</v>
       </c>
@@ -11084,7 +11084,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
         <v>306</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
         <v>306</v>
       </c>
@@ -11118,7 +11118,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
         <v>306</v>
       </c>
@@ -11135,7 +11135,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
         <v>306</v>
       </c>
@@ -11152,7 +11152,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
         <v>306</v>
       </c>
@@ -11169,7 +11169,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
         <v>306</v>
       </c>
@@ -11186,7 +11186,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
         <v>306</v>
       </c>
@@ -11203,7 +11203,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
         <v>306</v>
       </c>
@@ -11220,7 +11220,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
         <v>306</v>
       </c>
@@ -11237,7 +11237,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
         <v>306</v>
       </c>
@@ -11254,7 +11254,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
         <v>306</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
         <v>306</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
         <v>306</v>
       </c>
@@ -11305,7 +11305,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
         <v>306</v>
       </c>
@@ -11322,7 +11322,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
         <v>306</v>
       </c>
@@ -11339,7 +11339,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
         <v>306</v>
       </c>
@@ -11356,7 +11356,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
         <v>306</v>
       </c>
@@ -11373,7 +11373,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
         <v>306</v>
       </c>
@@ -11390,7 +11390,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
         <v>306</v>
       </c>
@@ -11407,7 +11407,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
         <v>306</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
         <v>306</v>
       </c>
@@ -11441,7 +11441,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
         <v>306</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A356" s="4" t="s">
         <v>306</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
         <v>306</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
         <v>306</v>
       </c>
@@ -11509,7 +11509,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
         <v>306</v>
       </c>
@@ -11526,7 +11526,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
         <v>306</v>
       </c>
@@ -11543,7 +11543,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
         <v>306</v>
       </c>
@@ -11560,7 +11560,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
         <v>306</v>
       </c>
@@ -11577,7 +11577,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
         <v>306</v>
       </c>
@@ -11594,7 +11594,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
         <v>306</v>
       </c>
@@ -11611,7 +11611,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
         <v>306</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A366" s="4" t="s">
         <v>306</v>
       </c>
@@ -11645,7 +11645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
         <v>306</v>
       </c>
@@ -11662,7 +11662,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
         <v>306</v>
       </c>
@@ -11679,7 +11679,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
         <v>306</v>
       </c>
@@ -11696,7 +11696,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
         <v>306</v>
       </c>
@@ -11713,7 +11713,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
         <v>306</v>
       </c>
@@ -11730,7 +11730,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
         <v>306</v>
       </c>
@@ -11747,7 +11747,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
         <v>306</v>
       </c>
@@ -11764,7 +11764,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
         <v>306</v>
       </c>
@@ -11781,7 +11781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
         <v>306</v>
       </c>
@@ -11798,7 +11798,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
         <v>306</v>
       </c>
@@ -11815,7 +11815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
         <v>306</v>
       </c>
@@ -11832,7 +11832,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
         <v>306</v>
       </c>
@@ -11849,7 +11849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
         <v>306</v>
       </c>
@@ -11866,7 +11866,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
         <v>306</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="112" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:5" ht="48" x14ac:dyDescent="0.35">
       <c r="A381" s="4" t="s">
         <v>306</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="112" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:5" ht="48" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
         <v>306</v>
       </c>
@@ -11913,7 +11913,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
         <v>306</v>
       </c>
@@ -11930,7 +11930,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
         <v>306</v>
       </c>
@@ -11947,7 +11947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A385" s="4" t="s">
         <v>306</v>
       </c>
@@ -11964,7 +11964,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
         <v>306</v>
       </c>
@@ -11981,7 +11981,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
         <v>306</v>
       </c>
@@ -11998,7 +11998,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
         <v>306</v>
       </c>
@@ -12015,7 +12015,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
         <v>306</v>
       </c>
@@ -12032,7 +12032,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
         <v>306</v>
       </c>
@@ -12049,7 +12049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
         <v>306</v>
       </c>
@@ -12066,7 +12066,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
         <v>306</v>
       </c>
@@ -12083,7 +12083,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
         <v>306</v>
       </c>
@@ -12100,7 +12100,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
         <v>306</v>
       </c>
@@ -12117,7 +12117,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
         <v>306</v>
       </c>
@@ -12134,7 +12134,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
         <v>306</v>
       </c>
@@ -12151,7 +12151,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
         <v>306</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
         <v>306</v>
       </c>
@@ -12185,7 +12185,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
         <v>306</v>
       </c>
@@ -12202,7 +12202,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
         <v>306</v>
       </c>
@@ -12219,7 +12219,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
         <v>306</v>
       </c>
@@ -12236,7 +12236,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A402" s="4" t="s">
         <v>306</v>
       </c>
@@ -12253,7 +12253,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
         <v>306</v>
       </c>
@@ -12270,7 +12270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A404" s="4" t="s">
         <v>306</v>
       </c>
@@ -12287,7 +12287,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A405" s="4" t="s">
         <v>306</v>
       </c>
@@ -12304,7 +12304,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A406" s="4" t="s">
         <v>306</v>
       </c>
@@ -12321,7 +12321,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
         <v>306</v>
       </c>
@@ -12338,7 +12338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A408" s="4" t="s">
         <v>306</v>
       </c>
@@ -12355,7 +12355,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A409" s="4" t="s">
         <v>306</v>
       </c>
@@ -12372,7 +12372,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
         <v>306</v>
       </c>
@@ -12389,7 +12389,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
         <v>306</v>
       </c>
@@ -12406,7 +12406,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
         <v>306</v>
       </c>
@@ -12423,7 +12423,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A413" s="4" t="s">
         <v>306</v>
       </c>
@@ -12440,7 +12440,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A414" s="4" t="s">
         <v>306</v>
       </c>
@@ -12457,7 +12457,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A415" s="4" t="s">
         <v>306</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A416" s="4" t="s">
         <v>306</v>
       </c>
@@ -12491,7 +12491,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A417" s="4" t="s">
         <v>306</v>
       </c>
@@ -12508,7 +12508,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A418" s="4" t="s">
         <v>306</v>
       </c>
@@ -12525,7 +12525,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A419" s="4" t="s">
         <v>306</v>
       </c>
@@ -12542,7 +12542,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A420" s="4" t="s">
         <v>306</v>
       </c>
@@ -12559,7 +12559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A421" s="4" t="s">
         <v>306</v>
       </c>
@@ -12576,7 +12576,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A422" s="4" t="s">
         <v>306</v>
       </c>
@@ -12593,7 +12593,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A423" s="4" t="s">
         <v>306</v>
       </c>
@@ -12610,7 +12610,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A424" s="4" t="s">
         <v>306</v>
       </c>
@@ -12627,7 +12627,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A425" s="4" t="s">
         <v>306</v>
       </c>
@@ -12644,7 +12644,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A426" s="4" t="s">
         <v>306</v>
       </c>
@@ -12661,7 +12661,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A427" s="4" t="s">
         <v>306</v>
       </c>
@@ -12678,7 +12678,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A428" s="4" t="s">
         <v>306</v>
       </c>
@@ -12695,7 +12695,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A429" s="4" t="s">
         <v>306</v>
       </c>
@@ -12712,7 +12712,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A430" s="4" t="s">
         <v>306</v>
       </c>
@@ -12729,7 +12729,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A431" s="4" t="s">
         <v>306</v>
       </c>
@@ -12746,7 +12746,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A432" s="4" t="s">
         <v>306</v>
       </c>
@@ -12763,7 +12763,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A433" s="4" t="s">
         <v>306</v>
       </c>
@@ -12780,7 +12780,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A434" s="4" t="s">
         <v>306</v>
       </c>
@@ -12797,7 +12797,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A435" s="4" t="s">
         <v>306</v>
       </c>
@@ -12814,7 +12814,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A436" s="4" t="s">
         <v>306</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A437" s="4" t="s">
         <v>306</v>
       </c>
@@ -12848,7 +12848,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A438" s="4" t="s">
         <v>306</v>
       </c>
@@ -12865,7 +12865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A439" s="4" t="s">
         <v>306</v>
       </c>
@@ -12882,7 +12882,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A440" s="4" t="s">
         <v>306</v>
       </c>
@@ -12899,7 +12899,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A441" s="4" t="s">
         <v>306</v>
       </c>
@@ -12916,7 +12916,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A442" s="4" t="s">
         <v>306</v>
       </c>
@@ -12933,7 +12933,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A443" s="4" t="s">
         <v>306</v>
       </c>
@@ -12950,7 +12950,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A444" s="4" t="s">
         <v>306</v>
       </c>
@@ -12967,7 +12967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A445" s="4" t="s">
         <v>306</v>
       </c>
@@ -12984,7 +12984,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A446" s="4" t="s">
         <v>306</v>
       </c>
@@ -13001,7 +13001,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A447" s="4" t="s">
         <v>306</v>
       </c>
@@ -13018,7 +13018,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A448" s="4" t="s">
         <v>306</v>
       </c>
@@ -13035,7 +13035,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A449" s="4" t="s">
         <v>306</v>
       </c>
@@ -13052,7 +13052,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A450" s="4" t="s">
         <v>306</v>
       </c>
@@ -13069,7 +13069,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A451" s="4" t="s">
         <v>306</v>
       </c>
@@ -13086,7 +13086,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A452" s="4" t="s">
         <v>306</v>
       </c>
@@ -13103,7 +13103,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A453" s="4" t="s">
         <v>306</v>
       </c>
@@ -13120,7 +13120,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A454" s="4" t="s">
         <v>306</v>
       </c>
@@ -13137,7 +13137,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A455" s="4" t="s">
         <v>306</v>
       </c>
@@ -13154,7 +13154,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A456" s="4" t="s">
         <v>306</v>
       </c>
@@ -13171,7 +13171,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A457" s="4" t="s">
         <v>306</v>
       </c>
@@ -13188,7 +13188,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A458" s="4" t="s">
         <v>306</v>
       </c>
@@ -13205,7 +13205,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A459" s="4" t="s">
         <v>306</v>
       </c>
@@ -13222,7 +13222,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A460" s="4" t="s">
         <v>306</v>
       </c>
@@ -13239,7 +13239,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A461" s="4" t="s">
         <v>306</v>
       </c>
@@ -13256,7 +13256,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A462" s="4" t="s">
         <v>306</v>
       </c>
@@ -13273,7 +13273,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A463" s="4" t="s">
         <v>306</v>
       </c>
@@ -13290,7 +13290,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A464" s="4" t="s">
         <v>306</v>
       </c>
@@ -13307,7 +13307,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A465" s="4" t="s">
         <v>306</v>
       </c>
@@ -13324,7 +13324,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A466" s="4" t="s">
         <v>306</v>
       </c>
@@ -13341,7 +13341,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A467" s="4" t="s">
         <v>306</v>
       </c>
@@ -13358,7 +13358,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A468" s="4" t="s">
         <v>306</v>
       </c>
@@ -13375,7 +13375,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A469" s="4" t="s">
         <v>306</v>
       </c>
@@ -13392,7 +13392,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A470" s="4" t="s">
         <v>306</v>
       </c>
@@ -13409,7 +13409,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A471" s="4" t="s">
         <v>306</v>
       </c>
@@ -13426,7 +13426,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A472" s="4" t="s">
         <v>306</v>
       </c>
@@ -13443,7 +13443,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A473" s="4" t="s">
         <v>306</v>
       </c>
@@ -13460,7 +13460,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A474" s="4" t="s">
         <v>306</v>
       </c>
@@ -13477,7 +13477,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A475" s="4" t="s">
         <v>306</v>
       </c>
@@ -13494,7 +13494,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A476" s="4" t="s">
         <v>306</v>
       </c>
@@ -13511,7 +13511,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="48" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A477" s="4" t="s">
         <v>306</v>
       </c>
@@ -13528,7 +13528,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A478" s="4" t="s">
         <v>306</v>
       </c>
@@ -13545,7 +13545,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A479" s="4" t="s">
         <v>306</v>
       </c>
@@ -13562,7 +13562,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A480" s="4" t="s">
         <v>306</v>
       </c>
@@ -13579,7 +13579,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A481" s="4" t="s">
         <v>306</v>
       </c>
@@ -13596,7 +13596,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A482" s="4" t="s">
         <v>306</v>
       </c>
@@ -13613,7 +13613,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A483" s="4" t="s">
         <v>306</v>
       </c>
@@ -13630,7 +13630,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A484" s="4" t="s">
         <v>306</v>
       </c>
@@ -13647,7 +13647,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A485" s="4" t="s">
         <v>306</v>
       </c>
@@ -13664,7 +13664,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A486" s="4" t="s">
         <v>306</v>
       </c>
@@ -13681,7 +13681,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A487" s="4" t="s">
         <v>306</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A488" s="4" t="s">
         <v>306</v>
       </c>
@@ -13715,7 +13715,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A489" s="4" t="s">
         <v>306</v>
       </c>
@@ -13732,7 +13732,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A490" s="4" t="s">
         <v>306</v>
       </c>
@@ -13749,7 +13749,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A491" s="4" t="s">
         <v>306</v>
       </c>
@@ -13766,7 +13766,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A492" s="4" t="s">
         <v>306</v>
       </c>
@@ -13783,7 +13783,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A493" s="4" t="s">
         <v>306</v>
       </c>
@@ -13800,7 +13800,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A494" s="4" t="s">
         <v>306</v>
       </c>
@@ -13817,7 +13817,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A495" s="4" t="s">
         <v>306</v>
       </c>
@@ -13834,7 +13834,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A496" s="4" t="s">
         <v>306</v>
       </c>
@@ -13851,7 +13851,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A497" s="4" t="s">
         <v>306</v>
       </c>
@@ -13868,7 +13868,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A498" s="4" t="s">
         <v>306</v>
       </c>
@@ -13885,7 +13885,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A499" s="4" t="s">
         <v>306</v>
       </c>
@@ -13902,7 +13902,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A500" s="4" t="s">
         <v>306</v>
       </c>
@@ -13919,7 +13919,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A501" s="4" t="s">
         <v>306</v>
       </c>
@@ -13936,7 +13936,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A502" s="4" t="s">
         <v>306</v>
       </c>
@@ -13953,7 +13953,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A503" s="4" t="s">
         <v>306</v>
       </c>
@@ -13970,7 +13970,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A504" s="4" t="s">
         <v>306</v>
       </c>
@@ -13987,7 +13987,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A505" s="4" t="s">
         <v>306</v>
       </c>
@@ -14004,7 +14004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="80" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A506" s="4" t="s">
         <v>306</v>
       </c>
@@ -14021,7 +14021,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A507" s="4" t="s">
         <v>306</v>
       </c>
@@ -14038,7 +14038,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A508" s="4" t="s">
         <v>306</v>
       </c>
@@ -14055,7 +14055,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A509" s="4" t="s">
         <v>306</v>
       </c>
@@ -14072,7 +14072,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A510" s="4" t="s">
         <v>306</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A511" s="4" t="s">
         <v>306</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A512" s="4" t="s">
         <v>306</v>
       </c>
@@ -14123,7 +14123,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A513" s="4" t="s">
         <v>306</v>
       </c>
@@ -14140,7 +14140,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A514" s="4" t="s">
         <v>306</v>
       </c>
@@ -14157,7 +14157,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A515" s="4" t="s">
         <v>306</v>
       </c>
@@ -14174,7 +14174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A516" s="4" t="s">
         <v>306</v>
       </c>
@@ -14191,7 +14191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A517" s="4" t="s">
         <v>306</v>
       </c>
@@ -14208,7 +14208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A518" s="4" t="s">
         <v>306</v>
       </c>
@@ -14225,7 +14225,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A519" s="4" t="s">
         <v>306</v>
       </c>
@@ -14242,7 +14242,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A520" s="4" t="s">
         <v>306</v>
       </c>
@@ -14259,7 +14259,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A521" s="4" t="s">
         <v>306</v>
       </c>
@@ -14276,7 +14276,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A522" s="4" t="s">
         <v>306</v>
       </c>
@@ -14293,7 +14293,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A523" s="4" t="s">
         <v>306</v>
       </c>
@@ -14310,7 +14310,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A524" s="4" t="s">
         <v>306</v>
       </c>
@@ -14327,7 +14327,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A525" s="4" t="s">
         <v>306</v>
       </c>
@@ -14344,7 +14344,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="32" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:5" ht="16" x14ac:dyDescent="0.35">
       <c r="A526" s="4" t="s">
         <v>306</v>
       </c>
@@ -14361,7 +14361,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A527" s="4" t="s">
         <v>306</v>
       </c>
@@ -14378,7 +14378,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A528" s="4" t="s">
         <v>306</v>
       </c>
@@ -14395,7 +14395,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A529" s="4" t="s">
         <v>306</v>
       </c>
@@ -14412,7 +14412,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A530" s="4" t="s">
         <v>306</v>
       </c>
@@ -14429,7 +14429,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A531" s="4" t="s">
         <v>306</v>
       </c>
@@ -14446,7 +14446,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A532" s="4" t="s">
         <v>306</v>
       </c>
@@ -14463,7 +14463,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A533" s="4" t="s">
         <v>306</v>
       </c>
@@ -14480,7 +14480,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A534" s="4" t="s">
         <v>306</v>
       </c>
@@ -14497,7 +14497,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A535" s="4" t="s">
         <v>306</v>
       </c>
@@ -14514,7 +14514,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="64" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:5" ht="32" x14ac:dyDescent="0.35">
       <c r="A536" s="4" t="s">
         <v>306</v>
       </c>
